--- a/output/alt_abbrev_annotation_using_abstract_df.xlsx
+++ b/output/alt_abbrev_annotation_using_abstract_df.xlsx
@@ -456,57 +456,57 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>captured</t>
+          <t>captured_status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>captured as:</t>
+          <t>captured_category_list</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PMIDs from Pubtator3</t>
+          <t>pubtator3_pmid</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Does alias represent gene in this publication?</t>
+          <t>alias_represent_gene_status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>As an Alternate Abbreviation?</t>
+          <t>alternate_abbreviation_status</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>How? I</t>
+          <t>simple_relationship_type</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>How? II</t>
+          <t>detailed_relationship_type</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>If not this gene, what is it?</t>
+          <t>alias_representation_details</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Text Location</t>
+          <t>relevant_text_section</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Relevant Text (surrounding)</t>
+          <t>relevant_text</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -577,11 +577,7 @@
           <t>mouse phenotype biomarker</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -643,12 +639,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -661,11 +657,7 @@
           <t>mouse phenotype biomarker</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -727,12 +719,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -745,11 +737,7 @@
           <t>mouse phenotype biomarker</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -811,24 +799,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>primer</t>
@@ -895,24 +875,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>primer</t>
@@ -982,24 +954,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>primer</t>
@@ -1070,24 +1034,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>primer</t>
@@ -1154,24 +1110,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>primer</t>
@@ -1238,28 +1186,28 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1321,24 +1269,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>primer</t>
@@ -1405,24 +1345,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>virus glycoprotein 58</t>
@@ -1489,24 +1421,16 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>glycoprotein B</t>
@@ -1573,24 +1497,16 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>glycoprotein gp58/116</t>
@@ -1657,24 +1573,16 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>gp58/116 complex of human cytomegalovirus (HCMV)</t>
@@ -1741,24 +1649,16 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>envelope (gp35 and gp58) proteins</t>
@@ -1825,24 +1725,16 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>human cytomegalovirus 58-kDa glycoprotein</t>
@@ -1909,24 +1801,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>human cytomegalovirus (CMV) membrane glycoprotein gp58/116 (gB</t>
@@ -1993,24 +1877,16 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>human cytomegalovirus glycoprotein B (gp58/116)</t>
@@ -2077,24 +1953,16 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>glycoproteins gp58/116 (gB)</t>
@@ -2161,24 +2029,16 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>glycoprotein(s) gp58-gp130</t>
@@ -2245,12 +2105,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2263,11 +2123,7 @@
           <t>derivative of HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>results</t>
@@ -2333,12 +2189,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2351,11 +2207,7 @@
           <t>derivative of HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>results</t>
@@ -2421,12 +2273,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2439,11 +2291,7 @@
           <t>derivative of HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -2505,12 +2353,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2523,11 +2371,7 @@
           <t>derivative of HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -2589,12 +2433,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2607,11 +2451,7 @@
           <t>HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>figure caption</t>
@@ -2673,12 +2513,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2691,14 +2531,10 @@
           <t>HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2757,12 +2593,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2775,14 +2611,10 @@
           <t>HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2841,12 +2673,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2859,14 +2691,10 @@
           <t>HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2925,12 +2753,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2943,14 +2771,10 @@
           <t>HGNC Previous Symbol</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3009,12 +2833,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3030,7 +2854,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Reviewers' Comments</t>
+          <t>reviewers' comments</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3089,12 +2913,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3107,11 +2931,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3173,12 +2993,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3191,11 +3011,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3257,12 +3073,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3275,11 +3091,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3341,12 +3153,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3359,11 +3171,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3425,12 +3233,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3443,11 +3251,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>results</t>
@@ -3509,12 +3313,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3527,11 +3331,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3593,12 +3393,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3611,11 +3411,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3677,12 +3473,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3695,11 +3491,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -3764,12 +3556,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3782,11 +3574,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -3848,12 +3636,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3866,11 +3654,7 @@
           <t>literature defined (uniprot protein short name)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>main text</t>
@@ -3932,12 +3716,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3950,11 +3734,7 @@
           <t>literature defined (uniprot alternative protein name)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -4016,29 +3796,25 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>main text</t>
@@ -4100,29 +3876,25 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -4184,29 +3956,25 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>main text</t>
@@ -4268,29 +4036,25 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -4352,32 +4116,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4436,32 +4196,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4520,12 +4276,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4538,14 +4294,10 @@
           <t>literature defined (uniprot alternative protein name)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4604,32 +4356,28 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4688,12 +4436,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4706,11 +4454,7 @@
           <t>literature defined (uniprot alternative protein name)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -4772,12 +4516,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4790,14 +4534,10 @@
           <t>literature defined</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4856,29 +4596,25 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>results</t>
@@ -4940,29 +4676,25 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -5026,29 +4758,25 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>main text</t>
@@ -5110,29 +4838,25 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>main text</t>
@@ -5194,29 +4918,25 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -5282,12 +5002,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5300,11 +5020,7 @@
           <t>literature defined</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>results</t>
@@ -5370,12 +5086,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5388,14 +5104,10 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5458,12 +5170,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5476,11 +5188,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -5546,29 +5254,25 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -5634,12 +5338,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5652,11 +5356,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>main text</t>
@@ -5722,29 +5422,25 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>results</t>
@@ -5811,12 +5507,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5829,11 +5525,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>results</t>
@@ -5899,12 +5591,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5917,14 +5609,10 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5987,12 +5675,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6005,11 +5693,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -6075,12 +5759,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6093,11 +5777,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -6163,12 +5843,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6181,11 +5861,7 @@
           <t>HCDM antigen nomenclature</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -6251,12 +5927,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6269,11 +5945,7 @@
           <t>literature defined (HGNC alias names)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -6339,24 +6011,16 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>scl-70, PM-scl</t>
@@ -6364,7 +6028,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6427,24 +6091,16 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>scl-70, PM-scl</t>
@@ -6452,7 +6108,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6515,24 +6171,16 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>scl-ab</t>
@@ -6603,24 +6251,16 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>superficial cell layers</t>
@@ -6691,24 +6331,16 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>scl100, scl75, scl70</t>
@@ -6779,24 +6411,16 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>small cell lung cancer</t>
@@ -6869,24 +6493,16 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>scl-70</t>
@@ -6894,7 +6510,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6959,24 +6575,16 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>spindle cell lipoma</t>
@@ -6984,7 +6592,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7049,24 +6657,16 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>scl-70, PM-scl</t>
@@ -7074,7 +6674,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7139,29 +6739,25 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -7227,29 +6823,25 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -7315,24 +6907,16 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>no mention of sur-2 or any variations in this publication. One mention of med23</t>
@@ -7403,32 +6987,28 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7487,29 +7067,25 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>results</t>
@@ -7575,12 +7151,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7593,14 +7169,10 @@
           <t>ortholog</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7659,12 +7231,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7677,11 +7249,7 @@
           <t>ortholog</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -7747,24 +7315,16 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>sulfonylurea (SUR) subunits, lit defined symbol for ABCC9</t>
@@ -7772,7 +7332,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7835,32 +7395,28 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7923,24 +7479,16 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>sulfonylurea (SUR) subunits, lit defined symbol for ABCC9</t>
@@ -7948,7 +7496,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8011,24 +7559,16 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Abp1p (autonomously replicating sequence-binding protein 1)</t>
@@ -8099,24 +7639,16 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>Abp1p (autonomously replicating sequence-binding protein 1)</t>
@@ -8187,24 +7719,16 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>Auxin-binding protein 1</t>
@@ -8275,24 +7799,16 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>androgen binding protein, lit defined symbol of SHBG</t>
@@ -8363,24 +7879,16 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>angiotensin binding protein (ABP1)</t>
@@ -8451,24 +7959,16 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>Abp(adhesion bonding proteins) adhesins</t>
@@ -8539,12 +8039,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8557,11 +8057,7 @@
           <t>ortholog</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>materials and methods</t>
@@ -8627,24 +8123,16 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>alternate abbreviation synonym for PABPC1</t>
@@ -8715,24 +8203,16 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>Albumin-Binding Peptides</t>
@@ -8803,24 +8283,16 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>Abp(adhesion bonding proteins) adhesins</t>
@@ -8891,12 +8363,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8909,14 +8381,10 @@
           <t>lit defined (HGNC alias)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8979,32 +8447,28 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9071,32 +8535,28 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9159,32 +8619,28 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9247,32 +8703,28 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9335,12 +8787,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9353,14 +8805,10 @@
           <t>lit defined (HGNC alias)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9423,12 +8871,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9441,14 +8889,10 @@
           <t>lit defined (HGNC alias)</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9514,32 +8958,28 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9605,32 +9045,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9693,32 +9129,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9780,24 +9212,16 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>global attention branch (GAB)</t>
@@ -9864,24 +9288,16 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>Guia Alimentar para a Populao</t>
@@ -9951,24 +9367,16 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>gestational age at birth (GAB)</t>
@@ -10035,24 +9443,16 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>dispatch SAPS/GAB/SAPS/MS 0019480381</t>
@@ -10122,24 +9522,16 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Initials of Ghazal Awais Butt </t>
@@ -10147,7 +9539,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>AuthorsÕ Contribution</t>
+          <t>authorsÕ contribution</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10209,24 +9601,16 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>GAB, gender attitudes about child problem behavior</t>
@@ -10234,7 +9618,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10293,24 +9677,16 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>group averaged BOIN (GAB)</t>
@@ -10318,7 +9694,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10377,24 +9753,16 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>_-aminobutyric acid (GABA)ergic</t>
@@ -10457,24 +9825,16 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>group A and B human respiratory syncytial virus</t>
@@ -10545,24 +9905,16 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>initials of  Guanai Bao</t>
@@ -10570,7 +9922,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>AuthorsÕ Contribution</t>
+          <t>authorsÕ contribution</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -10632,24 +9984,16 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>letters representing subunits</t>
@@ -10716,24 +10060,16 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>naming of figures</t>
@@ -10800,24 +10136,16 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>Alice city samples</t>
@@ -10884,24 +10212,16 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>hemoglobin subfractions</t>
@@ -10971,24 +10291,16 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>HNRNPA1 alias</t>
@@ -11055,24 +10367,16 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>blood antibodies</t>
@@ -11141,24 +10445,16 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>_1-adrenergic receptor blocker</t>
@@ -11229,24 +10525,16 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>genotype of rhinovirus</t>
@@ -11313,24 +10601,16 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>red blood cell type</t>
@@ -11400,12 +10680,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11415,14 +10695,10 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -11484,12 +10760,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11499,14 +10775,10 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -11568,24 +10840,16 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>aldosterone binding globulin</t>
@@ -11652,24 +10916,16 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
           <t>Bolio-Galvis A</t>
@@ -11677,7 +10933,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Author's contribution</t>
+          <t>authorsÕ contribution</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -11739,24 +10995,16 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>typo Adjustable gastric banding (AGB)</t>
@@ -11826,24 +11074,16 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
           <t>Agrobacterium sp. beta-glucosidase</t>
@@ -11910,12 +11150,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11925,14 +11165,10 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -11994,12 +11230,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -12009,14 +11245,10 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12078,12 +11310,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12093,14 +11325,10 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -12162,12 +11390,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12177,14 +11405,10 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12246,12 +11470,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12261,14 +11485,10 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12330,12 +11550,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12345,14 +11565,10 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -12414,12 +11630,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12429,14 +11645,10 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12498,12 +11710,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12513,14 +11725,10 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -12582,12 +11790,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12597,14 +11805,10 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12666,12 +11870,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12681,14 +11885,10 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12750,12 +11950,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12765,14 +11965,10 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -12834,12 +12030,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12849,14 +12045,10 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -12918,12 +12110,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12933,14 +12125,10 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -13006,24 +12194,16 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>amino acid</t>
@@ -13094,24 +12274,16 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>amino acid</t>
@@ -13185,24 +12357,16 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>amino acid</t>
@@ -13273,12 +12437,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13288,14 +12452,10 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -13361,12 +12521,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13379,11 +12539,7 @@
           <t>uniprot fiat</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -13445,12 +12601,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13458,11 +12614,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>isoglobotriaosylceramide vs isoglobotrihexosylceramide</t>
@@ -13532,12 +12684,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -13545,11 +12697,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>isoglobotriaosylceramide vs isoglobotrihexosylceramide</t>
@@ -13619,12 +12767,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -13632,11 +12780,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>isogloboside 3</t>
@@ -13703,12 +12847,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -13716,11 +12860,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>isoglobotriaosylceramide vs isoglobotrihexosylceramide</t>
@@ -13789,29 +12929,25 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -13873,12 +13009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -13888,14 +13024,10 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -13957,12 +13089,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -13972,14 +13104,10 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -14041,29 +13169,25 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -14125,29 +13249,25 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>discussion</t>
@@ -14209,12 +13329,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -14224,14 +13344,10 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>results</t>
@@ -14293,29 +13409,25 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -14377,22 +13489,22 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14462,22 +13574,22 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14546,22 +13658,22 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14630,29 +13742,25 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -14714,12 +13822,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -14729,14 +13837,10 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -14798,12 +13902,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -14813,14 +13917,10 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -14882,12 +13982,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -14897,14 +13997,10 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -14966,12 +14062,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14981,14 +14077,10 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -15050,12 +14142,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -15065,14 +14157,10 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>alternate abbreviation</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alternate Abbreviation</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -15134,29 +14222,25 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -15218,29 +14302,25 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -15302,29 +14382,25 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>introduction</t>
@@ -15386,29 +14462,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -15470,29 +14534,25 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Alias</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>abstract</t>
